--- a/EXCEL/Data/køn_stilling.xlsx
+++ b/EXCEL/Data/køn_stilling.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="83">
   <si>
     <t xml:space="preserve">Antal ansatte - </t>
   </si>
@@ -52,9 +52,6 @@
     <t>Personer Mænd</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ialt</t>
-  </si>
-  <si>
     <t>Ergo- Fysio- og Jordemødre, basis Reg.</t>
   </si>
   <si>
@@ -157,7 +154,7 @@
     <t>Datasæt 02 2020</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 12.58.45</t>
+    <t>Kørsel 8.4.2026 13.56.28</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
@@ -708,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="40" customWidth="1"/>
@@ -844,1968 +841,1374 @@
         <v>13</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="6">
-        <v>88063</v>
+        <v>1184</v>
       </c>
       <c r="D4" s="6">
-        <v>74246</v>
+        <v>1087</v>
       </c>
       <c r="E4" s="6">
-        <v>13817</v>
+        <v>97</v>
       </c>
       <c r="F4" s="6">
-        <v>90925</v>
+        <v>1319</v>
       </c>
       <c r="G4" s="6">
-        <v>76512</v>
+        <v>1203</v>
       </c>
       <c r="H4" s="6">
-        <v>14413</v>
+        <v>116</v>
       </c>
       <c r="I4" s="6">
-        <v>92255</v>
+        <v>1409</v>
       </c>
       <c r="J4" s="6">
-        <v>77392</v>
+        <v>1274</v>
       </c>
       <c r="K4" s="6">
-        <v>14863</v>
+        <v>135</v>
       </c>
       <c r="L4" s="6">
-        <v>90910</v>
+        <v>1423</v>
       </c>
       <c r="M4" s="6">
-        <v>76192</v>
+        <v>1277</v>
       </c>
       <c r="N4" s="6">
-        <v>14718</v>
+        <v>146</v>
       </c>
       <c r="O4" s="6">
-        <v>92191</v>
+        <v>1395</v>
       </c>
       <c r="P4" s="6">
-        <v>77245</v>
+        <v>1248</v>
       </c>
       <c r="Q4" s="6">
-        <v>14946</v>
+        <v>147</v>
       </c>
       <c r="R4" s="6">
-        <v>92510</v>
+        <v>1357</v>
       </c>
       <c r="S4" s="6">
-        <v>77415</v>
+        <v>1216</v>
       </c>
       <c r="T4" s="6">
-        <v>15095</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="8">
-        <v>4957</v>
+        <v>1876</v>
       </c>
       <c r="D5" s="8">
-        <v>4451</v>
+        <v>1470</v>
       </c>
       <c r="E5" s="8">
-        <v>506</v>
+        <v>406</v>
       </c>
       <c r="F5" s="8">
-        <v>5292</v>
+        <v>2043</v>
       </c>
       <c r="G5" s="8">
-        <v>4716</v>
+        <v>1585</v>
       </c>
       <c r="H5" s="8">
-        <v>576</v>
+        <v>458</v>
       </c>
       <c r="I5" s="8">
-        <v>5440</v>
+        <v>2137</v>
       </c>
       <c r="J5" s="8">
-        <v>4783</v>
+        <v>1617</v>
       </c>
       <c r="K5" s="8">
-        <v>657</v>
+        <v>520</v>
       </c>
       <c r="L5" s="8">
-        <v>5488</v>
+        <v>2122</v>
       </c>
       <c r="M5" s="8">
-        <v>4830</v>
+        <v>1612</v>
       </c>
       <c r="N5" s="8">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="O5" s="8">
-        <v>5512</v>
+        <v>2046</v>
       </c>
       <c r="P5" s="8">
-        <v>4866</v>
+        <v>1548</v>
       </c>
       <c r="Q5" s="8">
-        <v>646</v>
+        <v>498</v>
       </c>
       <c r="R5" s="8">
-        <v>5474</v>
+        <v>2008</v>
       </c>
       <c r="S5" s="8">
-        <v>4844</v>
+        <v>1521</v>
       </c>
       <c r="T5" s="8">
-        <v>630</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="6">
-        <v>1184</v>
+        <v>2422</v>
       </c>
       <c r="D6" s="6">
-        <v>1087</v>
+        <v>1743</v>
       </c>
       <c r="E6" s="6">
-        <v>97</v>
+        <v>679</v>
       </c>
       <c r="F6" s="6">
-        <v>1319</v>
+        <v>2765</v>
       </c>
       <c r="G6" s="6">
-        <v>1203</v>
+        <v>1988</v>
       </c>
       <c r="H6" s="6">
-        <v>116</v>
+        <v>777</v>
       </c>
       <c r="I6" s="6">
-        <v>1409</v>
+        <v>2906</v>
       </c>
       <c r="J6" s="6">
-        <v>1274</v>
+        <v>2065</v>
       </c>
       <c r="K6" s="6">
-        <v>135</v>
+        <v>841</v>
       </c>
       <c r="L6" s="6">
-        <v>1423</v>
+        <v>2856</v>
       </c>
       <c r="M6" s="6">
-        <v>1277</v>
+        <v>2078</v>
       </c>
       <c r="N6" s="6">
-        <v>146</v>
+        <v>778</v>
       </c>
       <c r="O6" s="6">
-        <v>1395</v>
+        <v>2822</v>
       </c>
       <c r="P6" s="6">
-        <v>1248</v>
+        <v>2058</v>
       </c>
       <c r="Q6" s="6">
-        <v>147</v>
+        <v>764</v>
       </c>
       <c r="R6" s="6">
-        <v>1357</v>
+        <v>2815</v>
       </c>
       <c r="S6" s="6">
-        <v>1216</v>
+        <v>2053</v>
       </c>
       <c r="T6" s="6">
-        <v>141</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" s="8">
-        <v>1876</v>
+        <v>455</v>
       </c>
       <c r="D7" s="8">
-        <v>1470</v>
+        <v>184</v>
       </c>
       <c r="E7" s="8">
-        <v>406</v>
+        <v>271</v>
       </c>
       <c r="F7" s="8">
-        <v>2043</v>
+        <v>441</v>
       </c>
       <c r="G7" s="8">
-        <v>1585</v>
+        <v>185</v>
       </c>
       <c r="H7" s="8">
-        <v>458</v>
+        <v>256</v>
       </c>
       <c r="I7" s="8">
-        <v>2137</v>
+        <v>439</v>
       </c>
       <c r="J7" s="8">
-        <v>1617</v>
+        <v>185</v>
       </c>
       <c r="K7" s="8">
-        <v>520</v>
+        <v>254</v>
       </c>
       <c r="L7" s="8">
-        <v>2122</v>
+        <v>450</v>
       </c>
       <c r="M7" s="8">
-        <v>1612</v>
+        <v>202</v>
       </c>
       <c r="N7" s="8">
-        <v>510</v>
+        <v>248</v>
       </c>
       <c r="O7" s="8">
-        <v>2046</v>
+        <v>451</v>
       </c>
       <c r="P7" s="8">
-        <v>1548</v>
+        <v>213</v>
       </c>
       <c r="Q7" s="8">
-        <v>498</v>
+        <v>238</v>
       </c>
       <c r="R7" s="8">
-        <v>2008</v>
+        <v>440</v>
       </c>
       <c r="S7" s="8">
-        <v>1521</v>
+        <v>216</v>
       </c>
       <c r="T7" s="8">
-        <v>487</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C8" s="6">
-        <v>2422</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>1743</v>
+        <v>0</v>
       </c>
       <c r="E8" s="6">
-        <v>679</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6">
-        <v>2765</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6">
-        <v>1988</v>
+        <v>0</v>
       </c>
       <c r="H8" s="6">
-        <v>777</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6">
-        <v>2906</v>
+        <v>0</v>
       </c>
       <c r="J8" s="6">
-        <v>2065</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>841</v>
+        <v>0</v>
       </c>
       <c r="L8" s="6">
-        <v>2856</v>
+        <v>44</v>
       </c>
       <c r="M8" s="6">
-        <v>2078</v>
+        <v>10</v>
       </c>
       <c r="N8" s="6">
-        <v>778</v>
+        <v>34</v>
       </c>
       <c r="O8" s="6">
-        <v>2822</v>
+        <v>44</v>
       </c>
       <c r="P8" s="6">
-        <v>2058</v>
+        <v>10</v>
       </c>
       <c r="Q8" s="6">
-        <v>764</v>
+        <v>34</v>
       </c>
       <c r="R8" s="6">
-        <v>2815</v>
+        <v>42</v>
       </c>
       <c r="S8" s="6">
-        <v>2053</v>
+        <v>9</v>
       </c>
       <c r="T8" s="6">
-        <v>762</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="8">
-        <v>2422</v>
+        <v>423</v>
       </c>
       <c r="D9" s="8">
-        <v>1743</v>
+        <v>155</v>
       </c>
       <c r="E9" s="8">
-        <v>679</v>
+        <v>268</v>
       </c>
       <c r="F9" s="8">
-        <v>2765</v>
+        <v>426</v>
       </c>
       <c r="G9" s="8">
-        <v>1988</v>
+        <v>155</v>
       </c>
       <c r="H9" s="8">
-        <v>777</v>
+        <v>271</v>
       </c>
       <c r="I9" s="8">
-        <v>2906</v>
+        <v>426</v>
       </c>
       <c r="J9" s="8">
-        <v>2065</v>
+        <v>159</v>
       </c>
       <c r="K9" s="8">
-        <v>841</v>
+        <v>267</v>
       </c>
       <c r="L9" s="8">
-        <v>2856</v>
+        <v>802</v>
       </c>
       <c r="M9" s="8">
-        <v>2078</v>
+        <v>392</v>
       </c>
       <c r="N9" s="8">
-        <v>778</v>
+        <v>410</v>
       </c>
       <c r="O9" s="8">
-        <v>2822</v>
+        <v>970</v>
       </c>
       <c r="P9" s="8">
-        <v>2058</v>
+        <v>487</v>
       </c>
       <c r="Q9" s="8">
-        <v>764</v>
+        <v>483</v>
       </c>
       <c r="R9" s="8">
-        <v>2815</v>
+        <v>1033</v>
       </c>
       <c r="S9" s="8">
-        <v>2053</v>
+        <v>533</v>
       </c>
       <c r="T9" s="8">
-        <v>762</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>6670</v>
+        <v>163</v>
       </c>
       <c r="D10" s="6">
-        <v>2834</v>
+        <v>29</v>
       </c>
       <c r="E10" s="6">
-        <v>3836</v>
+        <v>134</v>
       </c>
       <c r="F10" s="6">
-        <v>6834</v>
+        <v>173</v>
       </c>
       <c r="G10" s="6">
-        <v>2937</v>
+        <v>32</v>
       </c>
       <c r="H10" s="6">
-        <v>3897</v>
+        <v>141</v>
       </c>
       <c r="I10" s="6">
-        <v>7060</v>
+        <v>181</v>
       </c>
       <c r="J10" s="6">
-        <v>3112</v>
+        <v>37</v>
       </c>
       <c r="K10" s="6">
-        <v>3948</v>
+        <v>144</v>
       </c>
       <c r="L10" s="6">
-        <v>6952</v>
+        <v>159</v>
       </c>
       <c r="M10" s="6">
-        <v>3181</v>
+        <v>36</v>
       </c>
       <c r="N10" s="6">
-        <v>3771</v>
+        <v>123</v>
       </c>
       <c r="O10" s="6">
-        <v>7042</v>
+        <v>163</v>
       </c>
       <c r="P10" s="6">
-        <v>3295</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="6">
-        <v>3747</v>
+        <v>122</v>
       </c>
       <c r="R10" s="6">
-        <v>7139</v>
+        <v>168</v>
       </c>
       <c r="S10" s="6">
-        <v>3404</v>
+        <v>46</v>
       </c>
       <c r="T10" s="6">
-        <v>3735</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11" s="8">
-        <v>455</v>
+        <v>266</v>
       </c>
       <c r="D11" s="8">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="E11" s="8">
-        <v>271</v>
+        <v>201</v>
       </c>
       <c r="F11" s="8">
-        <v>441</v>
+        <v>228</v>
       </c>
       <c r="G11" s="8">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="H11" s="8">
-        <v>256</v>
+        <v>167</v>
       </c>
       <c r="I11" s="8">
-        <v>439</v>
+        <v>192</v>
       </c>
       <c r="J11" s="8">
-        <v>185</v>
+        <v>48</v>
       </c>
       <c r="K11" s="8">
-        <v>254</v>
+        <v>144</v>
       </c>
       <c r="L11" s="8">
-        <v>450</v>
+        <v>145</v>
       </c>
       <c r="M11" s="8">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="N11" s="8">
-        <v>248</v>
+        <v>111</v>
       </c>
       <c r="O11" s="8">
-        <v>451</v>
+        <v>121</v>
       </c>
       <c r="P11" s="8">
-        <v>213</v>
+        <v>38</v>
       </c>
       <c r="Q11" s="8">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="R11" s="8">
-        <v>440</v>
+        <v>104</v>
       </c>
       <c r="S11" s="8">
-        <v>216</v>
+        <v>33</v>
       </c>
       <c r="T11" s="8">
-        <v>224</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" s="6">
-        <v>0</v>
+        <v>5311</v>
       </c>
       <c r="D12" s="6">
-        <v>0</v>
+        <v>2392</v>
       </c>
       <c r="E12" s="6">
-        <v>0</v>
+        <v>2919</v>
       </c>
       <c r="F12" s="6">
-        <v>0</v>
+        <v>5461</v>
       </c>
       <c r="G12" s="6">
-        <v>0</v>
+        <v>2484</v>
       </c>
       <c r="H12" s="6">
-        <v>0</v>
+        <v>2977</v>
       </c>
       <c r="I12" s="6">
-        <v>0</v>
+        <v>5627</v>
       </c>
       <c r="J12" s="6">
-        <v>0</v>
+        <v>2635</v>
       </c>
       <c r="K12" s="6">
-        <v>0</v>
+        <v>2992</v>
       </c>
       <c r="L12" s="6">
-        <v>44</v>
+        <v>5300</v>
       </c>
       <c r="M12" s="6">
-        <v>10</v>
+        <v>2495</v>
       </c>
       <c r="N12" s="6">
-        <v>34</v>
+        <v>2805</v>
       </c>
       <c r="O12" s="6">
-        <v>44</v>
+        <v>5275</v>
       </c>
       <c r="P12" s="6">
-        <v>10</v>
+        <v>2500</v>
       </c>
       <c r="Q12" s="6">
-        <v>34</v>
+        <v>2775</v>
       </c>
       <c r="R12" s="6">
-        <v>42</v>
+        <v>5315</v>
       </c>
       <c r="S12" s="6">
-        <v>9</v>
+        <v>2550</v>
       </c>
       <c r="T12" s="6">
-        <v>33</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="8">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="D13" s="8">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="E13" s="8">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8">
-        <v>426</v>
+        <v>58</v>
       </c>
       <c r="G13" s="8">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="H13" s="8">
-        <v>271</v>
+        <v>48</v>
       </c>
       <c r="I13" s="8">
-        <v>426</v>
+        <v>148</v>
       </c>
       <c r="J13" s="8">
-        <v>159</v>
+        <v>37</v>
       </c>
       <c r="K13" s="8">
-        <v>267</v>
+        <v>111</v>
       </c>
       <c r="L13" s="8">
-        <v>802</v>
+        <v>33</v>
       </c>
       <c r="M13" s="8">
-        <v>392</v>
+        <v>7</v>
       </c>
       <c r="N13" s="8">
-        <v>410</v>
+        <v>26</v>
       </c>
       <c r="O13" s="8">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="P13" s="8">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="8">
-        <v>483</v>
+        <v>0</v>
       </c>
       <c r="R13" s="8">
-        <v>1033</v>
+        <v>24</v>
       </c>
       <c r="S13" s="8">
-        <v>533</v>
+        <v>12</v>
       </c>
       <c r="T13" s="8">
-        <v>500</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14" s="6">
-        <v>163</v>
+        <v>2166</v>
       </c>
       <c r="D14" s="6">
-        <v>29</v>
+        <v>1821</v>
       </c>
       <c r="E14" s="6">
-        <v>134</v>
+        <v>345</v>
       </c>
       <c r="F14" s="6">
-        <v>173</v>
+        <v>2410</v>
       </c>
       <c r="G14" s="6">
-        <v>32</v>
+        <v>2020</v>
       </c>
       <c r="H14" s="6">
-        <v>141</v>
+        <v>390</v>
       </c>
       <c r="I14" s="6">
-        <v>181</v>
+        <v>2484</v>
       </c>
       <c r="J14" s="6">
-        <v>37</v>
+        <v>2029</v>
       </c>
       <c r="K14" s="6">
-        <v>144</v>
+        <v>455</v>
       </c>
       <c r="L14" s="6">
-        <v>159</v>
+        <v>2491</v>
       </c>
       <c r="M14" s="6">
-        <v>36</v>
+        <v>2008</v>
       </c>
       <c r="N14" s="6">
-        <v>123</v>
+        <v>483</v>
       </c>
       <c r="O14" s="6">
-        <v>163</v>
+        <v>2512</v>
       </c>
       <c r="P14" s="6">
-        <v>41</v>
+        <v>1974</v>
       </c>
       <c r="Q14" s="6">
-        <v>122</v>
+        <v>538</v>
       </c>
       <c r="R14" s="6">
-        <v>168</v>
+        <v>2506</v>
       </c>
       <c r="S14" s="6">
-        <v>46</v>
+        <v>2026</v>
       </c>
       <c r="T14" s="6">
-        <v>122</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C15" s="8">
-        <v>266</v>
+        <v>8323</v>
       </c>
       <c r="D15" s="8">
-        <v>65</v>
+        <v>7429</v>
       </c>
       <c r="E15" s="8">
-        <v>201</v>
+        <v>894</v>
       </c>
       <c r="F15" s="8">
-        <v>228</v>
+        <v>8483</v>
       </c>
       <c r="G15" s="8">
-        <v>61</v>
+        <v>7592</v>
       </c>
       <c r="H15" s="8">
-        <v>167</v>
+        <v>891</v>
       </c>
       <c r="I15" s="8">
-        <v>192</v>
+        <v>9106</v>
       </c>
       <c r="J15" s="8">
-        <v>48</v>
+        <v>8169</v>
       </c>
       <c r="K15" s="8">
-        <v>144</v>
+        <v>937</v>
       </c>
       <c r="L15" s="8">
-        <v>145</v>
+        <v>8965</v>
       </c>
       <c r="M15" s="8">
-        <v>34</v>
+        <v>7999</v>
       </c>
       <c r="N15" s="8">
-        <v>111</v>
+        <v>966</v>
       </c>
       <c r="O15" s="8">
-        <v>121</v>
+        <v>9007</v>
       </c>
       <c r="P15" s="8">
-        <v>38</v>
+        <v>8050</v>
       </c>
       <c r="Q15" s="8">
-        <v>83</v>
+        <v>957</v>
       </c>
       <c r="R15" s="8">
-        <v>104</v>
+        <v>8713</v>
       </c>
       <c r="S15" s="8">
-        <v>33</v>
+        <v>7771</v>
       </c>
       <c r="T15" s="8">
-        <v>71</v>
+        <v>942</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C16" s="6">
-        <v>5311</v>
+        <v>3940</v>
       </c>
       <c r="D16" s="6">
-        <v>2392</v>
+        <v>2725</v>
       </c>
       <c r="E16" s="6">
-        <v>2919</v>
+        <v>1215</v>
       </c>
       <c r="F16" s="6">
-        <v>5461</v>
+        <v>3866</v>
       </c>
       <c r="G16" s="6">
-        <v>2484</v>
+        <v>2642</v>
       </c>
       <c r="H16" s="6">
-        <v>2977</v>
+        <v>1224</v>
       </c>
       <c r="I16" s="6">
-        <v>5627</v>
+        <v>4011</v>
       </c>
       <c r="J16" s="6">
-        <v>2635</v>
+        <v>2744</v>
       </c>
       <c r="K16" s="6">
-        <v>2992</v>
+        <v>1267</v>
       </c>
       <c r="L16" s="6">
-        <v>5300</v>
+        <v>4100</v>
       </c>
       <c r="M16" s="6">
-        <v>2495</v>
+        <v>2781</v>
       </c>
       <c r="N16" s="6">
-        <v>2805</v>
+        <v>1319</v>
       </c>
       <c r="O16" s="6">
-        <v>5275</v>
+        <v>4150</v>
       </c>
       <c r="P16" s="6">
-        <v>2500</v>
+        <v>2847</v>
       </c>
       <c r="Q16" s="6">
-        <v>2775</v>
+        <v>1303</v>
       </c>
       <c r="R16" s="6">
-        <v>5315</v>
+        <v>4132</v>
       </c>
       <c r="S16" s="6">
-        <v>2550</v>
+        <v>2801</v>
       </c>
       <c r="T16" s="6">
-        <v>2765</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C17" s="8">
-        <v>0</v>
+        <v>6059</v>
       </c>
       <c r="D17" s="8">
-        <v>0</v>
+        <v>6039</v>
       </c>
       <c r="E17" s="8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F17" s="8">
-        <v>58</v>
+        <v>6173</v>
       </c>
       <c r="G17" s="8">
-        <v>10</v>
+        <v>6146</v>
       </c>
       <c r="H17" s="8">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="I17" s="8">
-        <v>148</v>
+        <v>6072</v>
       </c>
       <c r="J17" s="8">
-        <v>37</v>
+        <v>6047</v>
       </c>
       <c r="K17" s="8">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="L17" s="8">
-        <v>33</v>
+        <v>5933</v>
       </c>
       <c r="M17" s="8">
-        <v>7</v>
+        <v>5908</v>
       </c>
       <c r="N17" s="8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O17" s="8">
-        <v>0</v>
+        <v>5705</v>
       </c>
       <c r="P17" s="8">
-        <v>0</v>
+        <v>5684</v>
       </c>
       <c r="Q17" s="8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R17" s="8">
-        <v>24</v>
+        <v>5429</v>
       </c>
       <c r="S17" s="8">
-        <v>12</v>
+        <v>5407</v>
       </c>
       <c r="T17" s="8">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" s="6">
-        <v>2166</v>
+        <v>1089</v>
       </c>
       <c r="D18" s="6">
-        <v>1821</v>
+        <v>1083</v>
       </c>
       <c r="E18" s="6">
-        <v>345</v>
+        <v>6</v>
       </c>
       <c r="F18" s="6">
-        <v>2410</v>
+        <v>1097</v>
       </c>
       <c r="G18" s="6">
-        <v>2020</v>
+        <v>1091</v>
       </c>
       <c r="H18" s="6">
-        <v>390</v>
+        <v>6</v>
       </c>
       <c r="I18" s="6">
-        <v>2484</v>
+        <v>1099</v>
       </c>
       <c r="J18" s="6">
-        <v>2029</v>
+        <v>1092</v>
       </c>
       <c r="K18" s="6">
-        <v>455</v>
+        <v>7</v>
       </c>
       <c r="L18" s="6">
-        <v>2491</v>
+        <v>1137</v>
       </c>
       <c r="M18" s="6">
-        <v>2008</v>
+        <v>1129</v>
       </c>
       <c r="N18" s="6">
-        <v>483</v>
+        <v>8</v>
       </c>
       <c r="O18" s="6">
-        <v>2512</v>
+        <v>1125</v>
       </c>
       <c r="P18" s="6">
-        <v>1974</v>
+        <v>1118</v>
       </c>
       <c r="Q18" s="6">
-        <v>538</v>
+        <v>7</v>
       </c>
       <c r="R18" s="6">
-        <v>2506</v>
+        <v>1131</v>
       </c>
       <c r="S18" s="6">
-        <v>2026</v>
+        <v>1124</v>
       </c>
       <c r="T18" s="6">
-        <v>480</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C19" s="8">
-        <v>2166</v>
+        <v>39125</v>
       </c>
       <c r="D19" s="8">
-        <v>1821</v>
+        <v>37232</v>
       </c>
       <c r="E19" s="8">
-        <v>345</v>
+        <v>1893</v>
       </c>
       <c r="F19" s="8">
-        <v>2410</v>
+        <v>39999</v>
       </c>
       <c r="G19" s="8">
-        <v>2020</v>
+        <v>38030</v>
       </c>
       <c r="H19" s="8">
-        <v>390</v>
+        <v>1969</v>
       </c>
       <c r="I19" s="8">
-        <v>2484</v>
+        <v>39780</v>
       </c>
       <c r="J19" s="8">
-        <v>2029</v>
+        <v>37854</v>
       </c>
       <c r="K19" s="8">
-        <v>455</v>
+        <v>1926</v>
       </c>
       <c r="L19" s="8">
-        <v>2491</v>
+        <v>38514</v>
       </c>
       <c r="M19" s="8">
-        <v>2008</v>
+        <v>36623</v>
       </c>
       <c r="N19" s="8">
-        <v>483</v>
+        <v>1891</v>
       </c>
       <c r="O19" s="8">
-        <v>2512</v>
+        <v>39466</v>
       </c>
       <c r="P19" s="8">
-        <v>1974</v>
+        <v>37457</v>
       </c>
       <c r="Q19" s="8">
-        <v>538</v>
+        <v>2009</v>
       </c>
       <c r="R19" s="8">
-        <v>2506</v>
+        <v>39686</v>
       </c>
       <c r="S19" s="8">
-        <v>2026</v>
+        <v>37622</v>
       </c>
       <c r="T19" s="8">
-        <v>480</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C20" s="6">
-        <v>8323</v>
+        <v>2000</v>
       </c>
       <c r="D20" s="6">
-        <v>7429</v>
+        <v>1880</v>
       </c>
       <c r="E20" s="6">
-        <v>894</v>
+        <v>120</v>
       </c>
       <c r="F20" s="6">
-        <v>8483</v>
+        <v>2033</v>
       </c>
       <c r="G20" s="6">
-        <v>7592</v>
+        <v>1910</v>
       </c>
       <c r="H20" s="6">
-        <v>891</v>
+        <v>123</v>
       </c>
       <c r="I20" s="6">
-        <v>9106</v>
+        <v>2048</v>
       </c>
       <c r="J20" s="6">
-        <v>8169</v>
+        <v>1922</v>
       </c>
       <c r="K20" s="6">
-        <v>937</v>
+        <v>126</v>
       </c>
       <c r="L20" s="6">
-        <v>8965</v>
+        <v>2039</v>
       </c>
       <c r="M20" s="6">
-        <v>7999</v>
+        <v>1915</v>
       </c>
       <c r="N20" s="6">
-        <v>966</v>
+        <v>124</v>
       </c>
       <c r="O20" s="6">
-        <v>9007</v>
+        <v>2031</v>
       </c>
       <c r="P20" s="6">
-        <v>8050</v>
+        <v>1911</v>
       </c>
       <c r="Q20" s="6">
-        <v>957</v>
+        <v>120</v>
       </c>
       <c r="R20" s="6">
-        <v>8713</v>
+        <v>1987</v>
       </c>
       <c r="S20" s="6">
-        <v>7771</v>
+        <v>1866</v>
       </c>
       <c r="T20" s="6">
-        <v>942</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C21" s="8">
-        <v>8323</v>
+        <v>2678</v>
       </c>
       <c r="D21" s="8">
-        <v>7429</v>
+        <v>1526</v>
       </c>
       <c r="E21" s="8">
-        <v>894</v>
+        <v>1152</v>
       </c>
       <c r="F21" s="8">
-        <v>8483</v>
+        <v>2828</v>
       </c>
       <c r="G21" s="8">
-        <v>7592</v>
+        <v>1651</v>
       </c>
       <c r="H21" s="8">
-        <v>891</v>
+        <v>1177</v>
       </c>
       <c r="I21" s="8">
-        <v>9106</v>
+        <v>2954</v>
       </c>
       <c r="J21" s="8">
-        <v>8169</v>
+        <v>1705</v>
       </c>
       <c r="K21" s="8">
-        <v>937</v>
+        <v>1249</v>
       </c>
       <c r="L21" s="8">
-        <v>8965</v>
+        <v>3017</v>
       </c>
       <c r="M21" s="8">
-        <v>7999</v>
+        <v>1751</v>
       </c>
       <c r="N21" s="8">
-        <v>966</v>
+        <v>1266</v>
       </c>
       <c r="O21" s="8">
-        <v>9007</v>
+        <v>3102</v>
       </c>
       <c r="P21" s="8">
-        <v>8050</v>
+        <v>1803</v>
       </c>
       <c r="Q21" s="8">
-        <v>957</v>
+        <v>1299</v>
       </c>
       <c r="R21" s="8">
-        <v>8713</v>
+        <v>3221</v>
       </c>
       <c r="S21" s="8">
-        <v>7771</v>
+        <v>1879</v>
       </c>
       <c r="T21" s="8">
-        <v>942</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C22" s="6">
-        <v>3940</v>
+        <v>6745</v>
       </c>
       <c r="D22" s="6">
-        <v>2725</v>
+        <v>4203</v>
       </c>
       <c r="E22" s="6">
-        <v>1215</v>
+        <v>2542</v>
       </c>
       <c r="F22" s="6">
-        <v>3866</v>
+        <v>7165</v>
       </c>
       <c r="G22" s="6">
-        <v>2642</v>
+        <v>4460</v>
       </c>
       <c r="H22" s="6">
-        <v>1224</v>
+        <v>2705</v>
       </c>
       <c r="I22" s="6">
-        <v>4011</v>
+        <v>7380</v>
       </c>
       <c r="J22" s="6">
-        <v>2744</v>
+        <v>4597</v>
       </c>
       <c r="K22" s="6">
-        <v>1267</v>
+        <v>2783</v>
       </c>
       <c r="L22" s="6">
-        <v>4100</v>
+        <v>7529</v>
       </c>
       <c r="M22" s="6">
-        <v>2781</v>
+        <v>4721</v>
       </c>
       <c r="N22" s="6">
-        <v>1319</v>
+        <v>2808</v>
       </c>
       <c r="O22" s="6">
-        <v>4150</v>
+        <v>7662</v>
       </c>
       <c r="P22" s="6">
-        <v>2847</v>
+        <v>4795</v>
       </c>
       <c r="Q22" s="6">
-        <v>1303</v>
+        <v>2867</v>
       </c>
       <c r="R22" s="6">
-        <v>4132</v>
+        <v>7953</v>
       </c>
       <c r="S22" s="6">
-        <v>2801</v>
+        <v>5008</v>
       </c>
       <c r="T22" s="6">
-        <v>1331</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C23" s="8">
-        <v>3940</v>
+        <v>1668</v>
       </c>
       <c r="D23" s="8">
-        <v>2725</v>
+        <v>1060</v>
       </c>
       <c r="E23" s="8">
-        <v>1215</v>
+        <v>608</v>
       </c>
       <c r="F23" s="8">
-        <v>3866</v>
+        <v>1743</v>
       </c>
       <c r="G23" s="8">
-        <v>2642</v>
+        <v>1093</v>
       </c>
       <c r="H23" s="8">
-        <v>1224</v>
+        <v>650</v>
       </c>
       <c r="I23" s="8">
-        <v>4011</v>
+        <v>1696</v>
       </c>
       <c r="J23" s="8">
-        <v>2744</v>
+        <v>1055</v>
       </c>
       <c r="K23" s="8">
-        <v>1267</v>
+        <v>641</v>
       </c>
       <c r="L23" s="8">
-        <v>4100</v>
+        <v>1670</v>
       </c>
       <c r="M23" s="8">
-        <v>2781</v>
+        <v>1050</v>
       </c>
       <c r="N23" s="8">
-        <v>1319</v>
+        <v>620</v>
       </c>
       <c r="O23" s="8">
-        <v>4150</v>
+        <v>1760</v>
       </c>
       <c r="P23" s="8">
-        <v>2847</v>
+        <v>1094</v>
       </c>
       <c r="Q23" s="8">
-        <v>1303</v>
+        <v>666</v>
       </c>
       <c r="R23" s="8">
-        <v>4132</v>
+        <v>1850</v>
       </c>
       <c r="S23" s="8">
-        <v>2801</v>
+        <v>1141</v>
       </c>
       <c r="T23" s="8">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="6">
-        <v>7369</v>
-      </c>
-      <c r="D24" s="6">
-        <v>7342</v>
-      </c>
-      <c r="E24" s="6">
-        <v>27</v>
-      </c>
-      <c r="F24" s="6">
-        <v>7507</v>
-      </c>
-      <c r="G24" s="6">
-        <v>7473</v>
-      </c>
-      <c r="H24" s="6">
-        <v>34</v>
-      </c>
-      <c r="I24" s="6">
-        <v>7390</v>
-      </c>
-      <c r="J24" s="6">
-        <v>7357</v>
-      </c>
-      <c r="K24" s="6">
-        <v>33</v>
-      </c>
-      <c r="L24" s="6">
-        <v>7289</v>
-      </c>
-      <c r="M24" s="6">
-        <v>7255</v>
-      </c>
-      <c r="N24" s="6">
-        <v>34</v>
-      </c>
-      <c r="O24" s="6">
-        <v>7125</v>
-      </c>
-      <c r="P24" s="6">
-        <v>7095</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>30</v>
-      </c>
-      <c r="R24" s="6">
-        <v>7034</v>
-      </c>
-      <c r="S24" s="6">
-        <v>7000</v>
-      </c>
-      <c r="T24" s="6">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="8">
-        <v>6059</v>
-      </c>
-      <c r="D25" s="8">
-        <v>6039</v>
-      </c>
-      <c r="E25" s="8">
-        <v>20</v>
-      </c>
-      <c r="F25" s="8">
-        <v>6173</v>
-      </c>
-      <c r="G25" s="8">
-        <v>6146</v>
-      </c>
-      <c r="H25" s="8">
-        <v>27</v>
-      </c>
-      <c r="I25" s="8">
-        <v>6072</v>
-      </c>
-      <c r="J25" s="8">
-        <v>6047</v>
-      </c>
-      <c r="K25" s="8">
-        <v>25</v>
-      </c>
-      <c r="L25" s="8">
-        <v>5933</v>
-      </c>
-      <c r="M25" s="8">
-        <v>5908</v>
-      </c>
-      <c r="N25" s="8">
-        <v>25</v>
-      </c>
-      <c r="O25" s="8">
-        <v>5705</v>
-      </c>
-      <c r="P25" s="8">
-        <v>5684</v>
-      </c>
-      <c r="Q25" s="8">
-        <v>21</v>
-      </c>
-      <c r="R25" s="8">
-        <v>5429</v>
-      </c>
-      <c r="S25" s="8">
-        <v>5407</v>
-      </c>
-      <c r="T25" s="8">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="6">
-        <v>1089</v>
-      </c>
-      <c r="D26" s="6">
-        <v>1083</v>
-      </c>
-      <c r="E26" s="6">
-        <v>6</v>
-      </c>
-      <c r="F26" s="6">
-        <v>1097</v>
-      </c>
-      <c r="G26" s="6">
-        <v>1091</v>
-      </c>
-      <c r="H26" s="6">
-        <v>6</v>
-      </c>
-      <c r="I26" s="6">
-        <v>1099</v>
-      </c>
-      <c r="J26" s="6">
-        <v>1092</v>
-      </c>
-      <c r="K26" s="6">
-        <v>7</v>
-      </c>
-      <c r="L26" s="6">
-        <v>1137</v>
-      </c>
-      <c r="M26" s="6">
-        <v>1129</v>
-      </c>
-      <c r="N26" s="6">
-        <v>8</v>
-      </c>
-      <c r="O26" s="6">
-        <v>1125</v>
-      </c>
-      <c r="P26" s="6">
-        <v>1118</v>
-      </c>
-      <c r="Q26" s="6">
-        <v>7</v>
-      </c>
-      <c r="R26" s="6">
-        <v>1131</v>
-      </c>
-      <c r="S26" s="6">
-        <v>1124</v>
-      </c>
-      <c r="T26" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="8">
-        <v>39125</v>
-      </c>
-      <c r="D27" s="8">
-        <v>37232</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1893</v>
-      </c>
-      <c r="F27" s="8">
-        <v>39999</v>
-      </c>
-      <c r="G27" s="8">
-        <v>38030</v>
-      </c>
-      <c r="H27" s="8">
-        <v>1969</v>
-      </c>
-      <c r="I27" s="8">
-        <v>39780</v>
-      </c>
-      <c r="J27" s="8">
-        <v>37854</v>
-      </c>
-      <c r="K27" s="8">
-        <v>1926</v>
-      </c>
-      <c r="L27" s="8">
-        <v>38514</v>
-      </c>
-      <c r="M27" s="8">
-        <v>36623</v>
-      </c>
-      <c r="N27" s="8">
-        <v>1891</v>
-      </c>
-      <c r="O27" s="8">
-        <v>39466</v>
-      </c>
-      <c r="P27" s="8">
-        <v>37457</v>
-      </c>
-      <c r="Q27" s="8">
-        <v>2009</v>
-      </c>
-      <c r="R27" s="8">
-        <v>39686</v>
-      </c>
-      <c r="S27" s="8">
-        <v>37622</v>
-      </c>
-      <c r="T27" s="8">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="6">
-        <v>39125</v>
-      </c>
-      <c r="D28" s="6">
-        <v>37232</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1893</v>
-      </c>
-      <c r="F28" s="6">
-        <v>39999</v>
-      </c>
-      <c r="G28" s="6">
-        <v>38030</v>
-      </c>
-      <c r="H28" s="6">
-        <v>1969</v>
-      </c>
-      <c r="I28" s="6">
-        <v>39780</v>
-      </c>
-      <c r="J28" s="6">
-        <v>37854</v>
-      </c>
-      <c r="K28" s="6">
-        <v>1926</v>
-      </c>
-      <c r="L28" s="6">
-        <v>38514</v>
-      </c>
-      <c r="M28" s="6">
-        <v>36623</v>
-      </c>
-      <c r="N28" s="6">
-        <v>1891</v>
-      </c>
-      <c r="O28" s="6">
-        <v>39466</v>
-      </c>
-      <c r="P28" s="6">
-        <v>37457</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>2009</v>
-      </c>
-      <c r="R28" s="6">
-        <v>39686</v>
-      </c>
-      <c r="S28" s="6">
-        <v>37622</v>
-      </c>
-      <c r="T28" s="6">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D29" s="8">
-        <v>1880</v>
-      </c>
-      <c r="E29" s="8">
-        <v>120</v>
-      </c>
-      <c r="F29" s="8">
-        <v>2033</v>
-      </c>
-      <c r="G29" s="8">
-        <v>1910</v>
-      </c>
-      <c r="H29" s="8">
-        <v>123</v>
-      </c>
-      <c r="I29" s="8">
-        <v>2048</v>
-      </c>
-      <c r="J29" s="8">
-        <v>1922</v>
-      </c>
-      <c r="K29" s="8">
-        <v>126</v>
-      </c>
-      <c r="L29" s="8">
-        <v>2039</v>
-      </c>
-      <c r="M29" s="8">
-        <v>1915</v>
-      </c>
-      <c r="N29" s="8">
-        <v>124</v>
-      </c>
-      <c r="O29" s="8">
-        <v>2031</v>
-      </c>
-      <c r="P29" s="8">
-        <v>1911</v>
-      </c>
-      <c r="Q29" s="8">
-        <v>120</v>
-      </c>
-      <c r="R29" s="8">
-        <v>1987</v>
-      </c>
-      <c r="S29" s="8">
-        <v>1866</v>
-      </c>
-      <c r="T29" s="8">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="6">
-        <v>2000</v>
-      </c>
-      <c r="D30" s="6">
-        <v>1880</v>
-      </c>
-      <c r="E30" s="6">
-        <v>120</v>
-      </c>
-      <c r="F30" s="6">
-        <v>2033</v>
-      </c>
-      <c r="G30" s="6">
-        <v>1910</v>
-      </c>
-      <c r="H30" s="6">
-        <v>123</v>
-      </c>
-      <c r="I30" s="6">
-        <v>2048</v>
-      </c>
-      <c r="J30" s="6">
-        <v>1922</v>
-      </c>
-      <c r="K30" s="6">
-        <v>126</v>
-      </c>
-      <c r="L30" s="6">
-        <v>2039</v>
-      </c>
-      <c r="M30" s="6">
-        <v>1915</v>
-      </c>
-      <c r="N30" s="6">
-        <v>124</v>
-      </c>
-      <c r="O30" s="6">
-        <v>2031</v>
-      </c>
-      <c r="P30" s="6">
-        <v>1911</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>120</v>
-      </c>
-      <c r="R30" s="6">
-        <v>1987</v>
-      </c>
-      <c r="S30" s="6">
-        <v>1866</v>
-      </c>
-      <c r="T30" s="6">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="8">
-        <v>11091</v>
-      </c>
-      <c r="D31" s="8">
-        <v>6789</v>
-      </c>
-      <c r="E31" s="8">
-        <v>4302</v>
-      </c>
-      <c r="F31" s="8">
-        <v>11736</v>
-      </c>
-      <c r="G31" s="8">
-        <v>7204</v>
-      </c>
-      <c r="H31" s="8">
-        <v>4532</v>
-      </c>
-      <c r="I31" s="8">
-        <v>12030</v>
-      </c>
-      <c r="J31" s="8">
-        <v>7357</v>
-      </c>
-      <c r="K31" s="8">
-        <v>4673</v>
-      </c>
-      <c r="L31" s="8">
-        <v>12216</v>
-      </c>
-      <c r="M31" s="8">
-        <v>7522</v>
-      </c>
-      <c r="N31" s="8">
-        <v>4694</v>
-      </c>
-      <c r="O31" s="8">
-        <v>12524</v>
-      </c>
-      <c r="P31" s="8">
-        <v>7692</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>4832</v>
-      </c>
-      <c r="R31" s="8">
-        <v>13024</v>
-      </c>
-      <c r="S31" s="8">
-        <v>8028</v>
-      </c>
-      <c r="T31" s="8">
-        <v>4996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="6">
-        <v>2678</v>
-      </c>
-      <c r="D32" s="6">
-        <v>1526</v>
-      </c>
-      <c r="E32" s="6">
-        <v>1152</v>
-      </c>
-      <c r="F32" s="6">
-        <v>2828</v>
-      </c>
-      <c r="G32" s="6">
-        <v>1651</v>
-      </c>
-      <c r="H32" s="6">
-        <v>1177</v>
-      </c>
-      <c r="I32" s="6">
-        <v>2954</v>
-      </c>
-      <c r="J32" s="6">
-        <v>1705</v>
-      </c>
-      <c r="K32" s="6">
-        <v>1249</v>
-      </c>
-      <c r="L32" s="6">
-        <v>3017</v>
-      </c>
-      <c r="M32" s="6">
-        <v>1751</v>
-      </c>
-      <c r="N32" s="6">
-        <v>1266</v>
-      </c>
-      <c r="O32" s="6">
-        <v>3102</v>
-      </c>
-      <c r="P32" s="6">
-        <v>1803</v>
-      </c>
-      <c r="Q32" s="6">
-        <v>1299</v>
-      </c>
-      <c r="R32" s="6">
-        <v>3221</v>
-      </c>
-      <c r="S32" s="6">
-        <v>1879</v>
-      </c>
-      <c r="T32" s="6">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="8">
-        <v>6745</v>
-      </c>
-      <c r="D33" s="8">
-        <v>4203</v>
-      </c>
-      <c r="E33" s="8">
-        <v>2542</v>
-      </c>
-      <c r="F33" s="8">
-        <v>7165</v>
-      </c>
-      <c r="G33" s="8">
-        <v>4460</v>
-      </c>
-      <c r="H33" s="8">
-        <v>2705</v>
-      </c>
-      <c r="I33" s="8">
-        <v>7380</v>
-      </c>
-      <c r="J33" s="8">
-        <v>4597</v>
-      </c>
-      <c r="K33" s="8">
-        <v>2783</v>
-      </c>
-      <c r="L33" s="8">
-        <v>7529</v>
-      </c>
-      <c r="M33" s="8">
-        <v>4721</v>
-      </c>
-      <c r="N33" s="8">
-        <v>2808</v>
-      </c>
-      <c r="O33" s="8">
-        <v>7662</v>
-      </c>
-      <c r="P33" s="8">
-        <v>4795</v>
-      </c>
-      <c r="Q33" s="8">
-        <v>2867</v>
-      </c>
-      <c r="R33" s="8">
-        <v>7953</v>
-      </c>
-      <c r="S33" s="8">
-        <v>5008</v>
-      </c>
-      <c r="T33" s="8">
-        <v>2945</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="6">
-        <v>1668</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1060</v>
-      </c>
-      <c r="E34" s="6">
-        <v>608</v>
-      </c>
-      <c r="F34" s="6">
-        <v>1743</v>
-      </c>
-      <c r="G34" s="6">
-        <v>1093</v>
-      </c>
-      <c r="H34" s="6">
-        <v>650</v>
-      </c>
-      <c r="I34" s="6">
-        <v>1696</v>
-      </c>
-      <c r="J34" s="6">
-        <v>1055</v>
-      </c>
-      <c r="K34" s="6">
-        <v>641</v>
-      </c>
-      <c r="L34" s="6">
-        <v>1670</v>
-      </c>
-      <c r="M34" s="6">
-        <v>1050</v>
-      </c>
-      <c r="N34" s="6">
-        <v>620</v>
-      </c>
-      <c r="O34" s="6">
-        <v>1760</v>
-      </c>
-      <c r="P34" s="6">
-        <v>1094</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>666</v>
-      </c>
-      <c r="R34" s="6">
-        <v>1850</v>
-      </c>
-      <c r="S34" s="6">
-        <v>1141</v>
-      </c>
-      <c r="T34" s="6">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2813,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2821,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2829,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2837,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2845,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2853,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2861,7 +2264,7 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2869,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2877,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2885,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2893,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2901,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2909,23 +2312,15 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>1</v>
-      </c>
-      <c r="B59" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2933,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2941,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2949,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2957,7 +2352,7 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2965,95 +2360,15 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>1</v>
-      </c>
-      <c r="B66" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>1</v>
-      </c>
-      <c r="B68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>76</v>
-      </c>
-      <c r="B71" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>1</v>
-      </c>
-      <c r="B72" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>1</v>
-      </c>
-      <c r="B73" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>1</v>
-      </c>
-      <c r="B74" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>1</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
         <v>82</v>
-      </c>
-      <c r="B78" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3065,7 +2380,7 @@
     <mergeCell ref="L2:N2"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A26:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
